--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_推計方法のバックテスト_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_推計方法のバックテスト_20260915.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_全設定" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分母の伸び" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_サービス別の趨勢" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要介護度別（川崎町方式）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="+0.00%;-0.00%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -51,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +158,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -919,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1259,57 +1285,57 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>据置</t>
+          <t>度別</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>75歳以上人口</t>
+          <t>要介護度別の認定者数（1号）</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
       <c r="F11" s="13" t="n">
-        <v>0.09886649583386194</v>
+        <v>0.136032603156596</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.05255655235684723</v>
+        <v>0.0982403830605643</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.0399</v>
+        <v>0.0076</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>0.0373</v>
+        <v>0.1482</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.08039999999999999</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>据置</t>
+          <t>度別</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>第1号被保険者数</t>
+          <t>要介護度別の認定者数（総数）</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="F12" s="13" t="n">
-        <v>0.09886649583386194</v>
+        <v>0.1340358528344311</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.05255655235684723</v>
+        <v>0.09730515004603835</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.0399</v>
+        <v>0.0106</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.0373</v>
+        <v>0.1466</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.08039999999999999</v>
+        <v>0.1347</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1346,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>認定者数</t>
+          <t>75歳以上人口</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1343,73 +1369,57 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>補正</t>
+          <t>据置</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>75歳以上人口</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n"/>
       <c r="F14" s="13" t="n">
-        <v>0.1015953669837398</v>
+        <v>0.09886649583386194</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.05576988918930074</v>
+        <v>0.05255655235684723</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.0374</v>
+        <v>0.0399</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.0428</v>
+        <v>0.0373</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.08710000000000001</v>
+        <v>0.08039999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>補正</t>
+          <t>据置</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>75歳以上人口</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>認定者数</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="F15" s="13" t="n">
-        <v>0.1026016355860789</v>
+        <v>0.09886649583386194</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.05589017443447827</v>
+        <v>0.05255655235684723</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.039</v>
+        <v>0.0399</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.0373</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.08039999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1427,25 +1437,25 @@
         <v>0.25</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.1008442910603487</v>
+        <v>0.1015953669837398</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.05593660483186846</v>
+        <v>0.05576988918930074</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0363</v>
+        <v>0.0374</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.0453</v>
+        <v>0.0428</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>0.0863</v>
+        <v>0.08710000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1460,28 +1470,28 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.1004098201224818</v>
+        <v>0.1026016355860789</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.05594777532598194</v>
+        <v>0.05589017443447827</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>0.0458</v>
+        <v>0.0397</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1496,28 +1506,28 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.1049679147940096</v>
+        <v>0.1008442910603487</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.05606877591496976</v>
+        <v>0.05593660483186846</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.0363</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.0453</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0863</v>
       </c>
     </row>
     <row r="19">
@@ -1532,28 +1542,28 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.1010452400747745</v>
+        <v>0.1004098201224818</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.05619375996788075</v>
+        <v>0.05594777532598194</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.0366</v>
+        <v>0.036</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0.0447</v>
+        <v>0.0458</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.0873</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1568,28 +1578,28 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.1001714213234507</v>
+        <v>0.1049679147940096</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.05620226437049965</v>
+        <v>0.05606877591496976</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0361</v>
+        <v>0.0405</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.0457</v>
+        <v>0.0369</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.0868</v>
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1604,28 +1614,28 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.1107586955031147</v>
+        <v>0.1010452400747745</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.05630569363077564</v>
+        <v>0.05619375996788075</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.042</v>
+        <v>0.0366</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0.0342</v>
+        <v>0.0447</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.09269999999999999</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="22">
@@ -1640,7 +1650,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="13" t="n">
         <v>0.02</v>
@@ -1649,19 +1659,19 @@
         <v>3</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.1000519655844196</v>
+        <v>0.1001714213234507</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.05647138731299006</v>
+        <v>0.05620226437049965</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0362</v>
+        <v>0.0361</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>0.0457</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>0.0876</v>
+        <v>0.0868</v>
       </c>
     </row>
     <row r="23">
@@ -1676,28 +1686,28 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.1013784599006503</v>
+        <v>0.1107586955031147</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.05647938558747434</v>
+        <v>0.05630569363077564</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.042</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>0.0442</v>
+        <v>0.0342</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.0883</v>
+        <v>0.09269999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1712,7 +1722,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="13" t="n">
         <v>0.02</v>
@@ -1721,10 +1731,10 @@
         <v>3</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.1005246034996707</v>
+        <v>0.1000519655844196</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.05675514415345376</v>
+        <v>0.05647138731299006</v>
       </c>
       <c r="H24" s="13" t="n">
         <v>0.0362</v>
@@ -1733,7 +1743,7 @@
         <v>0.0457</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="25">
@@ -1748,7 +1758,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D25" s="13" t="n">
         <v>0.03</v>
@@ -1757,19 +1767,19 @@
         <v>3</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.1033122789301248</v>
+        <v>0.1013784599006503</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.05679348169064954</v>
+        <v>0.05647938558747434</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0.0373</v>
+        <v>0.0369</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>0.0438</v>
+        <v>0.0442</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0883</v>
       </c>
     </row>
     <row r="26">
@@ -1780,11 +1790,11 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>第1号被保険者数</t>
+          <t>75歳以上人口</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D26" s="13" t="n">
         <v>0.02</v>
@@ -1793,19 +1803,19 @@
         <v>3</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.09920194276573498</v>
+        <v>0.1005246034996707</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.0532157346395801</v>
+        <v>0.05675514415345376</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.0362</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.0362</v>
+        <v>0.0457</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>0.083</v>
+        <v>0.08839999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1816,32 +1826,32 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>第1号被保険者数</t>
+          <t>75歳以上人口</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.1004139082604948</v>
+        <v>0.1033122789301248</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.05331457949541455</v>
+        <v>0.05679348169064954</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>0.0413</v>
+        <v>0.0373</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>0.0345</v>
+        <v>0.0438</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>0.0842</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1859,16 +1869,16 @@
         <v>0.25</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.09938440235932587</v>
+        <v>0.09920194276573498</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.05331713773127789</v>
+        <v>0.0532157346395801</v>
       </c>
       <c r="H28" s="13" t="n">
         <v>0.0405</v>
@@ -1877,7 +1887,7 @@
         <v>0.0362</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>0.0833</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="29">
@@ -1892,28 +1902,28 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.09931605457785216</v>
+        <v>0.1004139082604948</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.0536379988098068</v>
+        <v>0.05331457949541455</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>0.0403</v>
+        <v>0.0413</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>0.0366</v>
+        <v>0.0345</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="30">
@@ -1928,7 +1938,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>0.03</v>
@@ -1937,19 +1947,19 @@
         <v>3</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.09968358565789519</v>
+        <v>0.09938440235932587</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.05385690656153933</v>
+        <v>0.05331713773127789</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0403</v>
+        <v>0.0405</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.0366</v>
+        <v>0.0362</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="31">
@@ -1967,25 +1977,25 @@
         <v>0.5</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.1018086076697795</v>
+        <v>0.09931605457785216</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.05388120709142652</v>
+        <v>0.0536379988098068</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>0.042</v>
+        <v>0.0403</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>0.0333</v>
+        <v>0.0366</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>0.0864</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2000,28 +2010,28 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.09944896290954136</v>
+        <v>0.09968358565789519</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.05407454542969278</v>
+        <v>0.05385690656153933</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0401</v>
+        <v>0.0403</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0366</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.0851</v>
+        <v>0.08460000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2036,28 +2046,28 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.1000327042398943</v>
+        <v>0.1018086076697795</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.05442705940979712</v>
+        <v>0.05388120709142652</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>0.0372</v>
+        <v>0.0333</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0.0859</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="34">
@@ -2075,25 +2085,25 @@
         <v>0.75</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.1047481710318733</v>
+        <v>0.09944896290954136</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.05450763570704916</v>
+        <v>0.05407454542969278</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0426</v>
+        <v>0.0401</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.0322</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0.0886</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="35">
@@ -2108,28 +2118,28 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.09958307682020869</v>
+        <v>0.1000327042398943</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.054525374499238</v>
+        <v>0.05442705940979712</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0.04</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0.0375</v>
+        <v>0.0372</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>0.0861</v>
+        <v>0.0859</v>
       </c>
     </row>
     <row r="36">
@@ -2144,28 +2154,28 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.1029258452753736</v>
+        <v>0.1047481710318733</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.05502759627605144</v>
+        <v>0.05450763570704916</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.04</v>
+        <v>0.0426</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.0378</v>
+        <v>0.0322</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0.0872</v>
+        <v>0.0886</v>
       </c>
     </row>
     <row r="37">
@@ -2183,25 +2193,25 @@
         <v>1</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.1108013804304603</v>
+        <v>0.09958307682020869</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.05519386534228188</v>
+        <v>0.054525374499238</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>0.0433</v>
+        <v>0.04</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0.0314</v>
+        <v>0.0375</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0861</v>
       </c>
     </row>
     <row r="38">
@@ -2212,32 +2222,32 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>認定者数</t>
+          <t>第1号被保険者数</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.1103966339399577</v>
+        <v>0.1029258452753736</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.0639896368319639</v>
+        <v>0.05502759627605144</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.0331</v>
+        <v>0.04</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.053</v>
+        <v>0.0378</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0.1058</v>
+        <v>0.0872</v>
       </c>
     </row>
     <row r="39">
@@ -2248,11 +2258,11 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>認定者数</t>
+          <t>第1号被保険者数</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D39" s="13" t="n">
         <v>0.05</v>
@@ -2261,19 +2271,19 @@
         <v>3</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.110221089483833</v>
+        <v>0.1108013804304603</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.06585587937724798</v>
+        <v>0.05519386534228188</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>0.0284</v>
+        <v>0.0433</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.0314</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.1063</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2291,25 +2301,25 @@
         <v>1</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E40" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.10874840276586</v>
+        <v>0.1103966339399577</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.06597162835420356</v>
+        <v>0.0639896368319639</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0267</v>
+        <v>0.0331</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>0.1047</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="41">
@@ -2327,25 +2337,25 @@
         <v>0.75</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.1092489039837922</v>
+        <v>0.110221089483833</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.06738982878415385</v>
+        <v>0.06585587937724798</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>0.0236</v>
+        <v>0.0284</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>0.0731</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>0.1055</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="42">
@@ -2360,28 +2370,28 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.1103996541472447</v>
+        <v>0.10874840276586</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.06777816492645787</v>
+        <v>0.06597162835420356</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.0238</v>
+        <v>0.0267</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.0728</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>0.1068</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="43">
@@ -2396,28 +2406,28 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.1097467466237498</v>
+        <v>0.1092489039837922</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.06783094888481533</v>
+        <v>0.06738982878415385</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0.0223</v>
+        <v>0.0236</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>0.0761</v>
+        <v>0.0731</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.1052</v>
+        <v>0.1055</v>
       </c>
     </row>
     <row r="44">
@@ -2432,28 +2442,28 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E44" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.1100074564733257</v>
+        <v>0.1103996541472447</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.06880307295562386</v>
+        <v>0.06777816492645787</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.0203</v>
+        <v>0.0238</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.0803</v>
+        <v>0.0728</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>0.1058</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="45">
@@ -2468,28 +2478,28 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E45" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.1097629882179546</v>
+        <v>0.1097467466237498</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.06883243504121232</v>
+        <v>0.06783094888481533</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>0.0205</v>
+        <v>0.0223</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0761</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>0.1062</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="46">
@@ -2504,28 +2514,28 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.1106763768458899</v>
+        <v>0.1100074564733257</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.06975649347959308</v>
+        <v>0.06880307295562386</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.0191</v>
+        <v>0.0203</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0.08289999999999999</v>
+        <v>0.0803</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.1073</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="47">
@@ -2543,25 +2553,25 @@
         <v>0.5</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E47" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.1105395228150938</v>
+        <v>0.1097629882179546</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0697871003378665</v>
+        <v>0.06883243504121232</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.0183</v>
+        <v>0.0205</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0.1065</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="48">
@@ -2579,25 +2589,25 @@
         <v>0.25</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E48" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.1109718148196274</v>
+        <v>0.1106763768458899</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.07029944712537876</v>
+        <v>0.06975649347959308</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.0175</v>
+        <v>0.0191</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0.0864</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>0.107</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="49">
@@ -2612,7 +2622,7 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D49" s="13" t="n">
         <v>0.02</v>
@@ -2621,18 +2631,90 @@
         <v>3</v>
       </c>
       <c r="F49" s="13" t="n">
+        <v>0.1105395228150938</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.0697871003378665</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>0.08460000000000001</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>補正</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>認定者数</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.1109718148196274</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.07029944712537876</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>補正</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>認定者数</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="13" t="n">
         <v>0.111625610733277</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G51" s="13" t="n">
         <v>0.07078303103154304</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.0164</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.08890000000000001</v>
       </c>
-      <c r="J49" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.1071</v>
       </c>
     </row>
@@ -3879,4 +3961,561 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>川崎町 第10期で用いている方式を小野町のデータで測る</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>方式：基準年度の要介護度別給付費（年報 様式2）に、要介護度別の認定者数の伸び（年報 様式1の5）を乗じて足し上げる。1人当たりの水準は基準年度で据え置く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>当方の方式が第1号被保険者1人当たりの利用率を延ばすのに対し、こちらは要介護度の構成の変化だけを織り込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>■ 要介護度別の認定者数（年報 様式1の5・総数・年度末）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>令和3年度</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>令和4年度</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>158</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>158</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>■ 伸び率（基準年度＝1.000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>起点→予測先</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度→令和6年度</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>1.027</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度→令和7年度</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>0.862</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>令和6年度→令和7年度</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <v>0.839</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>■ 総給付費の予測（価格調整後・千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>起点→予測先</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>要介護度別（川崎町方式）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>誤差</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>利用率・第1号・窓3年（当方）</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>誤差</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>断層をまたぐか</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度→令和6年度</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>1085998</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1074449</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>-0.01063462573692131</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1053548</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>-0.02988093592888297</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>またがない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度→令和7年度</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>1005144</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>857807</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>-0.1465828671568659</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1038467</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>0.03315229183968804</v>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>またぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>令和6年度→令和7年度</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>1005144</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>869753</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>-0.1346979572443279</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1041742</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0.03641065363432072</v>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>またぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>**※ 川崎町方式は、断層をまたがない令和5年度→令和6年度では▲1.06％と全方式のなかで最も良い。**いっぽう令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>**※ 理由は伸び率の表にある。**令和6年度→令和7年度の認定者数は要介護4が0.755倍、要介護5が0.626倍であるのに対し、給付費の実績は7.4％しか下がっていない。令和7年9月の断層で重度の認定者が「減った」のは計上の変更であって、その方々がサービスを使わなくなったわけではない。要介護度別の伸びをそのまま給付費に乗せると、この差がそのまま誤差になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>※ したがって本方式は、**断層の原因が町の確認で解消するまでは小野町には用いない。**解消した場合は、要介護度の構成の変化を織り込める点で当方の方式より優れる可能性があり、そのときに採り直す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>※ 認定者数を総数で見るか第1号で見るかによる差は小さい（総給付費の誤差9.73％と9.82％）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_推計方法のバックテスト_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_推計方法のバックテスト_20260915.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_全設定" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分母の伸び" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_サービス別の趨勢" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要介護度別（川崎町方式）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要介護度別（他町村の案件①方式）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の『サービス見込量算定の手引き』第5章の手順で、推計方法を小野町の年報の実績で検証しました。</t>
+          <t>他団体の『サービス見込量算定の手引き』第5章の手順で、推計方法を小野町の年報の実績で検証しました。</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>川崎町 第10期で用いている方式を小野町のデータで測る</t>
+          <t>他町村の案件①で用いている方式を小野町のデータで測る</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>要介護度別（川崎町方式）</t>
+          <t>要介護度別（他町村の案件①方式）</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4490,7 +4490,7 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>**※ 川崎町方式は、断層をまたがない令和5年度→令和6年度では▲1.06％と全方式のなかで最も良い。**いっぽう令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。</t>
+          <t>**※ 他町村の案件①方式は、断層をまたがない令和5年度→令和6年度では▲1.06％と全方式のなかで最も良い。**いっぽう令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。</t>
         </is>
       </c>
     </row>
